--- a/groo 산출물/2. Groo 요구사항정의서.xlsx
+++ b/groo 산출물/2. Groo 요구사항정의서.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="1716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1732">
   <si>
     <t>요구사항정의서</t>
   </si>
@@ -14371,6 +14371,210 @@
   </si>
   <si>
     <t>벤 관리 게시판은 엑셀로 출력 할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좌측 Nav가 있어야한다.
+공지사항
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다.
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+자유게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다.
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+공부게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">좌측 Nav가 있어야한다.
+공지사항
+- 게시판번호, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t>게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다.
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+자유게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t>- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t xml:space="preserve">
+공부게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">좌측 Nav가 있어야한다.
+공지사항
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다.
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+자유게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다.
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+공부게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+베스트게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">좌측 Nav가 있어야한다.
+공지사항
+- 게시판번호, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t>게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다.
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+자유게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 페이지 수 목록, 이전페이지, 다음페이지가 있어야 한다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t>- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+      </rPr>
+      <t xml:space="preserve">
+공부게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+- 게시물에 대해 댓글, 신고, 좋아요를 할 수 있어야 한다.
+베스트게시판
+- 게시판번호, 게시물 제목, 게시자, 작성일, 조회수, 댓글, 좋아요가 보여야 한다.
+- 해당게시물을 누르면 상세페이지로 이동한다,
+</t>
+    </r>
+  </si>
+  <si>
+    <t>GR-A04-003</t>
+  </si>
+  <si>
+    <t>GR-A04-004</t>
+  </si>
+  <si>
+    <t>GR-A04-005</t>
+  </si>
+  <si>
+    <t>신고받은 팀을 해제할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>신고받은 팀을 확인할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>신고받은 팀을 제재할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>팀 관리는 전체팀을 보여줘야한다.</t>
+  </si>
+  <si>
+    <t>팀 관리는 전체팀 활성되고 있는 팀을 보여줘야 한다.</t>
+  </si>
+  <si>
+    <t>팀 관리는 비활성화된 팀을 보여줘야 한다.</t>
+  </si>
+  <si>
+    <t>팀을 삭제 할 수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>부적절한 팀을 올린 유저에게 조치를 취해야 한다.</t>
+  </si>
+  <si>
+    <t>신고받은 팀을 벤 할수 있어야 한다.</t>
   </si>
 </sst>
 </file>
@@ -15728,7 +15932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="663">
+  <cellXfs count="664">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -17717,6 +17921,9 @@
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="141">
@@ -19289,7 +19496,7 @@
     <row r="50" spans="1:20">
       <c r="A50" s="437"/>
       <c r="B50" s="437" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C50" s="438" t="s">
         <v>1261</v>
@@ -19309,12 +19516,12 @@
       <c r="J50" s="434"/>
       <c r="K50" s="434"/>
     </row>
-    <row r="51" spans="1:20" ht="256.200000" customHeight="1">
+    <row r="51" spans="1:20" ht="319.800000" customHeight="1">
       <c r="A51" s="437"/>
       <c r="B51" s="437"/>
       <c r="C51" s="438"/>
-      <c r="D51" s="659" t="s">
-        <v>1686</v>
+      <c r="D51" s="663" t="s">
+        <v>1719</v>
       </c>
       <c r="E51" s="434" t="s">
         <v>24</v>
@@ -19940,7 +20147,7 @@
         <v>1429</v>
       </c>
       <c r="B74" s="434" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C74" s="438" t="s">
         <v>1092</v>
@@ -20010,7 +20217,7 @@
         <v>1430</v>
       </c>
       <c r="B77" s="434" t="s">
-        <v>336</v>
+        <v>1419</v>
       </c>
       <c r="C77" s="434" t="s">
         <v>1432</v>
@@ -20029,6 +20236,7 @@
       <c r="K77" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L77" s="460"/>
       <c r="M77" s="459"/>
     </row>
     <row r="78" spans="1:20" ht="17.250000" customHeight="1">
@@ -20049,6 +20257,7 @@
       <c r="K78" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L78" s="460"/>
       <c r="M78" s="459"/>
     </row>
     <row r="79" spans="1:20" ht="17.250000" customHeight="1">
@@ -20069,6 +20278,7 @@
       <c r="K79" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L79" s="460"/>
       <c r="M79" s="459"/>
     </row>
     <row r="80" spans="1:20" ht="17.250000" customHeight="1">
@@ -20089,12 +20299,13 @@
       <c r="K80" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L80" s="460"/>
       <c r="M80" s="459"/>
     </row>
     <row r="81" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A81" s="437"/>
       <c r="B81" s="434" t="s">
-        <v>339</v>
+        <v>1424</v>
       </c>
       <c r="C81" s="434" t="s">
         <v>1425</v>
@@ -20113,6 +20324,7 @@
       <c r="K81" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L81" s="460"/>
       <c r="M81" s="459"/>
     </row>
     <row r="82" spans="1:13" ht="17.250000" customHeight="1">
@@ -20133,6 +20345,7 @@
       <c r="K82" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L82" s="460"/>
       <c r="M82" s="459"/>
     </row>
     <row r="83" spans="1:13" ht="17.250000" customHeight="1">
@@ -20153,6 +20366,7 @@
       <c r="K83" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L83" s="460"/>
       <c r="M83" s="459"/>
     </row>
     <row r="84" spans="1:13" ht="17.250000" customHeight="1">
@@ -20173,6 +20387,7 @@
       <c r="K84" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L84" s="460"/>
       <c r="M84" s="459"/>
     </row>
     <row r="85" spans="1:13" ht="17.250000" customHeight="1">
@@ -20193,6 +20408,7 @@
       <c r="K85" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L85" s="460"/>
       <c r="M85" s="459"/>
     </row>
     <row r="86" spans="1:13" ht="17.250000" customHeight="1">
@@ -20213,6 +20429,7 @@
       <c r="K86" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L86" s="460"/>
       <c r="M86" s="459"/>
     </row>
     <row r="87" spans="1:13" ht="17.250000" customHeight="1">
@@ -20233,6 +20450,7 @@
       <c r="K87" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L87" s="460"/>
       <c r="M87" s="459"/>
     </row>
     <row r="88" spans="1:13" ht="17.250000" customHeight="1">
@@ -20253,6 +20471,7 @@
       <c r="K88" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L88" s="460"/>
       <c r="M88" s="459"/>
     </row>
     <row r="89" spans="1:13" ht="17.250000" customHeight="1">
@@ -20273,6 +20492,7 @@
       <c r="K89" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L89" s="460"/>
       <c r="M89" s="459"/>
     </row>
     <row r="90" spans="1:13" ht="17.250000" customHeight="1">
@@ -20293,6 +20513,7 @@
       <c r="K90" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L90" s="460"/>
       <c r="M90" s="459"/>
     </row>
     <row r="91" spans="1:13" ht="17.250000" customHeight="1">
@@ -20313,14 +20534,15 @@
       <c r="K91" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L91" s="460"/>
       <c r="M91" s="459"/>
     </row>
     <row r="92" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A92" s="437"/>
-      <c r="B92" s="446" t="s">
-        <v>344</v>
-      </c>
-      <c r="C92" s="446" t="s">
+      <c r="B92" s="437" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C92" s="437" t="s">
         <v>1435</v>
       </c>
       <c r="D92" s="295" t="s">
@@ -20337,12 +20559,13 @@
       <c r="K92" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L92" s="460"/>
       <c r="M92" s="459"/>
     </row>
     <row r="93" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A93" s="437"/>
-      <c r="B93" s="447"/>
-      <c r="C93" s="447"/>
+      <c r="B93" s="437"/>
+      <c r="C93" s="437"/>
       <c r="D93" s="295" t="s">
         <v>795</v>
       </c>
@@ -20357,12 +20580,13 @@
       <c r="K93" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L93" s="460"/>
       <c r="M93" s="459"/>
     </row>
     <row r="94" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A94" s="437"/>
-      <c r="B94" s="447"/>
-      <c r="C94" s="447"/>
+      <c r="B94" s="437"/>
+      <c r="C94" s="437"/>
       <c r="D94" s="295" t="s">
         <v>797</v>
       </c>
@@ -20382,8 +20606,8 @@
     </row>
     <row r="95" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A95" s="437"/>
-      <c r="B95" s="447"/>
-      <c r="C95" s="447"/>
+      <c r="B95" s="437"/>
+      <c r="C95" s="437"/>
       <c r="D95" s="295" t="s">
         <v>788</v>
       </c>
@@ -20403,8 +20627,8 @@
     </row>
     <row r="96" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A96" s="437"/>
-      <c r="B96" s="447"/>
-      <c r="C96" s="447"/>
+      <c r="B96" s="437"/>
+      <c r="C96" s="437"/>
       <c r="D96" s="295" t="s">
         <v>816</v>
       </c>
@@ -20424,8 +20648,8 @@
     </row>
     <row r="97" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A97" s="437"/>
-      <c r="B97" s="447"/>
-      <c r="C97" s="447"/>
+      <c r="B97" s="437"/>
+      <c r="C97" s="437"/>
       <c r="D97" s="295" t="s">
         <v>976</v>
       </c>
@@ -20445,8 +20669,8 @@
     </row>
     <row r="98" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A98" s="437"/>
-      <c r="B98" s="448"/>
-      <c r="C98" s="448"/>
+      <c r="B98" s="437"/>
+      <c r="C98" s="437"/>
       <c r="D98" s="295" t="s">
         <v>975</v>
       </c>
@@ -20467,7 +20691,7 @@
     <row r="99" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A99" s="437"/>
       <c r="B99" s="437" t="s">
-        <v>334</v>
+        <v>1721</v>
       </c>
       <c r="C99" s="437" t="s">
         <v>1714</v>
@@ -20486,6 +20710,7 @@
       <c r="K99" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L99" s="460"/>
     </row>
     <row r="100" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A100" s="437"/>
@@ -20505,6 +20730,7 @@
       <c r="K100" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L100" s="460"/>
     </row>
     <row r="101" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A101" s="437"/>
@@ -20524,6 +20750,7 @@
       <c r="K101" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L101" s="460"/>
     </row>
     <row r="102" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A102" s="437"/>
@@ -20543,6 +20770,7 @@
       <c r="K102" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L102" s="460"/>
     </row>
     <row r="103" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A103" s="437"/>
@@ -20562,6 +20790,7 @@
       <c r="K103" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L103" s="460"/>
     </row>
     <row r="104" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A104" s="437"/>
@@ -20581,6 +20810,7 @@
       <c r="K104" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L104" s="460"/>
     </row>
     <row r="105" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A105" s="437"/>
@@ -20600,39 +20830,164 @@
       <c r="K105" s="434" t="s">
         <v>170</v>
       </c>
+      <c r="L105" s="460"/>
     </row>
     <row r="106" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A106" s="464"/>
+      <c r="A106" s="437"/>
+      <c r="B106" s="437" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C106" s="437" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D106" s="295" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E106" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F106" s="434"/>
+      <c r="G106" s="434"/>
+      <c r="H106" s="434"/>
+      <c r="I106" s="434"/>
+      <c r="J106" s="434"/>
+      <c r="K106" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="L106" s="460"/>
     </row>
     <row r="107" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A107" s="464"/>
+      <c r="A107" s="437"/>
+      <c r="B107" s="437"/>
+      <c r="C107" s="437"/>
+      <c r="D107" s="295" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E107" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F107" s="434"/>
+      <c r="G107" s="434"/>
+      <c r="H107" s="434"/>
+      <c r="I107" s="434"/>
+      <c r="J107" s="434"/>
+      <c r="K107" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="L107" s="460"/>
     </row>
     <row r="108" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A108" s="464"/>
-      <c r="C108" s="463"/>
-      <c r="D108" s="464"/>
-      <c r="F108" s="463"/>
-      <c r="G108" s="463"/>
-      <c r="H108" s="463"/>
-      <c r="I108" s="463"/>
-      <c r="J108" s="463"/>
-      <c r="K108" s="463"/>
+      <c r="A108" s="437"/>
+      <c r="B108" s="437"/>
+      <c r="C108" s="437"/>
+      <c r="D108" s="295" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E108" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F108" s="434"/>
+      <c r="G108" s="434"/>
+      <c r="H108" s="434"/>
+      <c r="I108" s="434"/>
+      <c r="J108" s="434"/>
+      <c r="K108" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="L108" s="460"/>
     </row>
     <row r="109" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A109" s="464"/>
+      <c r="A109" s="437"/>
+      <c r="B109" s="437"/>
+      <c r="C109" s="437"/>
+      <c r="D109" s="295" t="s">
+        <v>1729</v>
+      </c>
+      <c r="E109" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F109" s="434"/>
+      <c r="G109" s="434"/>
+      <c r="H109" s="434"/>
+      <c r="I109" s="434"/>
+      <c r="J109" s="434"/>
+      <c r="K109" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="L109" s="460"/>
     </row>
     <row r="110" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A110" s="464"/>
+      <c r="A110" s="437"/>
+      <c r="B110" s="437"/>
+      <c r="C110" s="437"/>
+      <c r="D110" s="295" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E110" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F110" s="434"/>
+      <c r="G110" s="434"/>
+      <c r="H110" s="434"/>
+      <c r="I110" s="434"/>
+      <c r="J110" s="434"/>
+      <c r="K110" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="L110" s="460"/>
     </row>
     <row r="111" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A111" s="464"/>
+      <c r="A111" s="437"/>
+      <c r="B111" s="437"/>
+      <c r="C111" s="437"/>
+      <c r="D111" s="295" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E111" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F111" s="434"/>
+      <c r="G111" s="434"/>
+      <c r="H111" s="434"/>
+      <c r="I111" s="434"/>
+      <c r="J111" s="434"/>
+      <c r="K111" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="L111" s="460"/>
     </row>
     <row r="112" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A112" s="464"/>
+      <c r="A112" s="437"/>
+      <c r="B112" s="437"/>
+      <c r="C112" s="437"/>
+      <c r="D112" s="295" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E112" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F112" s="434"/>
+      <c r="G112" s="434"/>
+      <c r="H112" s="434"/>
+      <c r="I112" s="434"/>
+      <c r="J112" s="434"/>
+      <c r="K112" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="L112" s="460"/>
     </row>
     <row r="113" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A113" s="464"/>
+      <c r="B113" s="463"/>
+      <c r="C113" s="311"/>
+      <c r="D113" s="311"/>
       <c r="E113" s="311"/>
+      <c r="F113" s="311"/>
+      <c r="G113" s="311"/>
+      <c r="H113" s="311"/>
+      <c r="I113" s="311"/>
+      <c r="J113" s="311"/>
+      <c r="K113" s="311"/>
     </row>
     <row r="114" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A114" s="464"/>
@@ -24305,7 +24660,7 @@
       <c r="A505" s="464"/>
     </row>
   </sheetData>
-  <mergeCells count="126">
+  <mergeCells count="128">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:K2"/>
@@ -24342,7 +24697,7 @@
     <mergeCell ref="A74:A76"/>
     <mergeCell ref="B74:B76"/>
     <mergeCell ref="C74:C76"/>
-    <mergeCell ref="A77:A105"/>
+    <mergeCell ref="A77:A112"/>
     <mergeCell ref="B77:B80"/>
     <mergeCell ref="C77:C80"/>
     <mergeCell ref="B81:B91"/>
@@ -24351,6 +24706,8 @@
     <mergeCell ref="C92:C98"/>
     <mergeCell ref="B99:B105"/>
     <mergeCell ref="C99:C105"/>
+    <mergeCell ref="B106:B112"/>
+    <mergeCell ref="C106:C112"/>
     <mergeCell ref="B134:C134"/>
     <mergeCell ref="E375:K375"/>
     <mergeCell ref="E376:K376"/>

--- a/groo 산출물/2. Groo 요구사항정의서.xlsx
+++ b/groo 산출물/2. Groo 요구사항정의서.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="400" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="390" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="View 정의서" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="1733">
   <si>
     <t>요구사항정의서</t>
   </si>
@@ -14575,6 +14575,16 @@
   </si>
   <si>
     <t>신고받은 팀을 벤 할수 있어야 한다.</t>
+  </si>
+  <si>
+    <t>대시보드
+- 일정표 : 달력으로 스터디의 일정이나 투표 등등을 보여준다.
+- 일정표의 스케줄을 누르면 해당 스터디 상세페이지로 갈 수 있어야 한다.
+스터디 관리
+- 내 스터디 : 내가 가입되어 있는 스터디를 보여준다. 
+- 내가 소속한 스터디 게시글 : 내가 소속한 스터디 게시글에 대해 볼 수 있어야 한다.
+설정
+- 계정정보 : 간단한 정보를 수정할 수 있고 상세내역을 수정하려면 회원상세페이지로 보내야한다.</t>
   </si>
 </sst>
 </file>
@@ -15932,7 +15942,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="664">
+  <cellXfs count="663">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -17921,9 +17931,6 @@
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="141">
@@ -19186,7 +19193,7 @@
       <c r="B36" s="437"/>
       <c r="C36" s="438"/>
       <c r="D36" s="295" t="s">
-        <v>1692</v>
+        <v>1732</v>
       </c>
       <c r="E36" s="434" t="s">
         <v>24</v>
@@ -19520,7 +19527,7 @@
       <c r="A51" s="437"/>
       <c r="B51" s="437"/>
       <c r="C51" s="438"/>
-      <c r="D51" s="663" t="s">
+      <c r="D51" s="659" t="s">
         <v>1719</v>
       </c>
       <c r="E51" s="434" t="s">
@@ -20236,7 +20243,6 @@
       <c r="K77" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L77" s="460"/>
       <c r="M77" s="459"/>
     </row>
     <row r="78" spans="1:20" ht="17.250000" customHeight="1">
@@ -20257,7 +20263,6 @@
       <c r="K78" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L78" s="460"/>
       <c r="M78" s="459"/>
     </row>
     <row r="79" spans="1:20" ht="17.250000" customHeight="1">
@@ -20278,7 +20283,6 @@
       <c r="K79" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L79" s="460"/>
       <c r="M79" s="459"/>
     </row>
     <row r="80" spans="1:20" ht="17.250000" customHeight="1">
@@ -20299,7 +20303,6 @@
       <c r="K80" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L80" s="460"/>
       <c r="M80" s="459"/>
     </row>
     <row r="81" spans="1:13" ht="17.250000" customHeight="1">
@@ -20324,7 +20327,6 @@
       <c r="K81" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L81" s="460"/>
       <c r="M81" s="459"/>
     </row>
     <row r="82" spans="1:13" ht="17.250000" customHeight="1">
@@ -20345,7 +20347,6 @@
       <c r="K82" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L82" s="460"/>
       <c r="M82" s="459"/>
     </row>
     <row r="83" spans="1:13" ht="17.250000" customHeight="1">
@@ -20366,7 +20367,6 @@
       <c r="K83" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L83" s="460"/>
       <c r="M83" s="459"/>
     </row>
     <row r="84" spans="1:13" ht="17.250000" customHeight="1">
@@ -20387,7 +20387,6 @@
       <c r="K84" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L84" s="460"/>
       <c r="M84" s="459"/>
     </row>
     <row r="85" spans="1:13" ht="17.250000" customHeight="1">
@@ -20408,7 +20407,6 @@
       <c r="K85" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L85" s="460"/>
       <c r="M85" s="459"/>
     </row>
     <row r="86" spans="1:13" ht="17.250000" customHeight="1">
@@ -20429,7 +20427,6 @@
       <c r="K86" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L86" s="460"/>
       <c r="M86" s="459"/>
     </row>
     <row r="87" spans="1:13" ht="17.250000" customHeight="1">
@@ -20450,7 +20447,6 @@
       <c r="K87" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L87" s="460"/>
       <c r="M87" s="459"/>
     </row>
     <row r="88" spans="1:13" ht="17.250000" customHeight="1">
@@ -20471,7 +20467,6 @@
       <c r="K88" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L88" s="460"/>
       <c r="M88" s="459"/>
     </row>
     <row r="89" spans="1:13" ht="17.250000" customHeight="1">
@@ -20492,7 +20487,6 @@
       <c r="K89" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L89" s="460"/>
       <c r="M89" s="459"/>
     </row>
     <row r="90" spans="1:13" ht="17.250000" customHeight="1">
@@ -20513,7 +20507,6 @@
       <c r="K90" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L90" s="460"/>
       <c r="M90" s="459"/>
     </row>
     <row r="91" spans="1:13" ht="17.250000" customHeight="1">
@@ -20534,7 +20527,6 @@
       <c r="K91" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L91" s="460"/>
       <c r="M91" s="459"/>
     </row>
     <row r="92" spans="1:13" ht="17.250000" customHeight="1">
@@ -20559,7 +20551,6 @@
       <c r="K92" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L92" s="460"/>
       <c r="M92" s="459"/>
     </row>
     <row r="93" spans="1:13" ht="17.250000" customHeight="1">
@@ -20580,7 +20571,6 @@
       <c r="K93" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L93" s="460"/>
       <c r="M93" s="459"/>
     </row>
     <row r="94" spans="1:13" ht="17.250000" customHeight="1">
@@ -20710,7 +20700,6 @@
       <c r="K99" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L99" s="460"/>
     </row>
     <row r="100" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A100" s="437"/>
@@ -20730,7 +20719,6 @@
       <c r="K100" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L100" s="460"/>
     </row>
     <row r="101" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A101" s="437"/>
@@ -20750,7 +20738,6 @@
       <c r="K101" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L101" s="460"/>
     </row>
     <row r="102" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A102" s="437"/>
@@ -20770,7 +20757,6 @@
       <c r="K102" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L102" s="460"/>
     </row>
     <row r="103" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A103" s="437"/>
@@ -20790,7 +20776,6 @@
       <c r="K103" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L103" s="460"/>
     </row>
     <row r="104" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A104" s="437"/>
@@ -20810,7 +20795,6 @@
       <c r="K104" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L104" s="460"/>
     </row>
     <row r="105" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A105" s="437"/>
@@ -20830,7 +20814,6 @@
       <c r="K105" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L105" s="460"/>
     </row>
     <row r="106" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A106" s="437"/>
@@ -20854,7 +20837,6 @@
       <c r="K106" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L106" s="460"/>
     </row>
     <row r="107" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A107" s="437"/>
@@ -20874,7 +20856,6 @@
       <c r="K107" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L107" s="460"/>
     </row>
     <row r="108" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A108" s="437"/>
@@ -20894,7 +20875,6 @@
       <c r="K108" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L108" s="460"/>
     </row>
     <row r="109" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A109" s="437"/>
@@ -20914,7 +20894,6 @@
       <c r="K109" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L109" s="460"/>
     </row>
     <row r="110" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A110" s="437"/>
@@ -20934,7 +20913,6 @@
       <c r="K110" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L110" s="460"/>
     </row>
     <row r="111" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A111" s="437"/>
@@ -20954,7 +20932,6 @@
       <c r="K111" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L111" s="460"/>
     </row>
     <row r="112" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A112" s="437"/>
@@ -20974,20 +20951,10 @@
       <c r="K112" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="L112" s="460"/>
     </row>
     <row r="113" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A113" s="464"/>
-      <c r="B113" s="463"/>
-      <c r="C113" s="311"/>
-      <c r="D113" s="311"/>
       <c r="E113" s="311"/>
-      <c r="F113" s="311"/>
-      <c r="G113" s="311"/>
-      <c r="H113" s="311"/>
-      <c r="I113" s="311"/>
-      <c r="J113" s="311"/>
-      <c r="K113" s="311"/>
     </row>
     <row r="114" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A114" s="464"/>

--- a/groo 산출물/2. Groo 요구사항정의서.xlsx
+++ b/groo 산출물/2. Groo 요구사항정의서.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="1733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="1739">
   <si>
     <t>요구사항정의서</t>
   </si>
@@ -14585,6 +14585,64 @@
 - 내가 소속한 스터디 게시글 : 내가 소속한 스터디 게시글에 대해 볼 수 있어야 한다.
 설정
 - 계정정보 : 간단한 정보를 수정할 수 있고 상세내역을 수정하려면 회원상세페이지로 보내야한다.</t>
+  </si>
+  <si>
+    <t>대시보드
+- 일정표 : 달력으로 스터디의 일정이나 투표 등등을 보여준다.
+- 일정표의 스케줄을 누르면 해당 스터디 상세페이지로 갈 수 있어야 한다.
+나의 활동
+- 내 스터디 : 내가 가입되어 있는 스터디를 보여준다. 
+- 내가 소속한 스터디 게시글 : 내가 소속한 스터디 게시글에 대해 볼 수 있어야 한다.
+설정
+- 계정정보 : 간단한 정보를 수정할 수 있고 상세내역을 수정하려면 회원상세페이지로 보내야한다.</t>
+  </si>
+  <si>
+    <t>대시보드
+- 일정표 : 달력으로 스터디의 일정이나 투표 등등을 보여준다.
+- 일정표의 스케줄을 누르면 해당 스터디 상세페이지로 갈 수 있어야 한다.
+나의 활동
+- 내가 쓴 게시물  : 나의 게시글을 보여준다
+- 내가 소속한 스터디 게시글 : 내가 소속한 스터디 게시글에 대해 볼 수 있어야 한다.
+설정
+- 계정정보 : 간단한 정보를 수정할 수 있고 상세내역을 수정하려면 회원상세페이지로 보내야한다.</t>
+  </si>
+  <si>
+    <t>대시보드
+- 일정표 : 달력으로 스터디의 일정이나 투표 등등을 보여준다.
+- 일정표의 스케줄을 누르면 해당 스터디 상세페이지로 갈 수 있어야 한다.
+나의 활동
+- 내가 쓴 게시물  : 나의 게시글을 보여준다,
+- 내가 소속한 스터디 게시글 : 내가 소속한 스터디 게시글에 대해 볼 수 있어야 한다.
+설정
+- 계정정보 : 간단한 정보를 수정할 수 있고 상세내역을 수정하려면 회원상세페이지로 보내야한다.</t>
+  </si>
+  <si>
+    <t>대시보드
+- 일정표 : 달력으로 스터디의 일정이나 투표 등등을 보여준다.
+- 일정표의 스케줄을 누르면 해당 스터디 상세페이지로 갈 수 있어야 한다.
+나의 활동
+- 내가 쓴 게시물  : 나의 게시글을 보여준다,
+- 나의 리뷰 
+설정
+- 계정정보 : 간단한 정보를 수정할 수 있고 상세내역을 수정하려면 회원상세페이지로 보내야한다.</t>
+  </si>
+  <si>
+    <t>대시보드
+- 일정표 : 달력으로 스터디의 일정이나 투표 등등을 보여준다.
+- 일정표의 스케줄을 누르면 해당 스터디 상세페이지로 갈 수 있어야 한다.
+나의 활동
+- 내가 쓴 게시물  : 나의 게시글을 보여준다,
+- 나의 리뷰 : 나의 리뷰를 보여준다.
+설정
+- 계정정보 : 간단한 정보를 수정할 수 있고 상세내역을 수정하려면 회원상세페이지로 보내야한다.</t>
+  </si>
+  <si>
+    <t>대시보드
+- 일정표 : 달력으로 스터디의 일정이나 투표 등등을 보여준다.
+- 일정표의 스케줄을 누르면 해당 스터디 상세페이지로 갈 수 있어야 한다.
+나의 활동
+- 내가 쓴 게시물  : 나의 게시글을 보여준다,
+- 나의 리뷰 : 나의 리뷰를 보여준다.</t>
   </si>
 </sst>
 </file>
@@ -19193,7 +19251,7 @@
       <c r="B36" s="437"/>
       <c r="C36" s="438"/>
       <c r="D36" s="295" t="s">
-        <v>1732</v>
+        <v>1738</v>
       </c>
       <c r="E36" s="434" t="s">
         <v>24</v>

--- a/groo 산출물/2. Groo 요구사항정의서.xlsx
+++ b/groo 산출물/2. Groo 요구사항정의서.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="390" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="380" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="View 정의서" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="1739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1746">
   <si>
     <t>요구사항정의서</t>
   </si>
@@ -14643,6 +14643,32 @@
 나의 활동
 - 내가 쓴 게시물  : 나의 게시글을 보여준다,
 - 나의 리뷰 : 나의 리뷰를 보여준다.</t>
+  </si>
+  <si>
+    <t>아이디, 비밀번호를 찾을 수 있는 방법이 있어야 한다.</t>
+  </si>
+  <si>
+    <t>게시판을 누르면 게시판 목록으로 이동해야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비회원이 로그인을 누르면 로그인 페이지로 이동해야 한다. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비회원이 로그인을 누르면 로그인 페이지로 이동해야 한다.
+</t>
+  </si>
+  <si>
+    <t>비회원이 로그인을 누르면 로그인 페이지로 이동해야 한다.
+비회원이 회원가입을 누르면 회원가입 페이지로 이동해야 한다.</t>
+  </si>
+  <si>
+    <t>인기, 신규스터디를 보여주고 해당 스터디를 눌렀을때 
+스터디 상세페이지로 이동한다.</t>
+  </si>
+  <si>
+    <t>활동중인 스터디를 보여주고 해당 스터디를 눌렀을때 
+스터디 상세페이지로 이동한다.</t>
   </si>
 </sst>
 </file>
@@ -16000,7 +16026,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="663">
+  <cellXfs count="666">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -17989,6 +18015,15 @@
     </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="141">
@@ -18425,7 +18460,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T505"/>
+  <dimension ref="A1:XFD505"/>
   <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="311" width="22.87999916" customWidth="1" outlineLevel="0"/>
@@ -18517,13 +18552,13 @@
       <c r="N3" s="460"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="437" t="s">
+      <c r="A4" s="446" t="s">
         <v>1427</v>
       </c>
-      <c r="B4" s="437" t="s">
+      <c r="B4" s="446" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="437" t="s">
+      <c r="C4" s="446" t="s">
         <v>437</v>
       </c>
       <c r="D4" s="28" t="s">
@@ -18544,9 +18579,9 @@
       <c r="N4" s="460"/>
     </row>
     <row r="5" spans="1:14" ht="28.500000" customHeight="1">
-      <c r="A5" s="437"/>
-      <c r="B5" s="437"/>
-      <c r="C5" s="437"/>
+      <c r="A5" s="447"/>
+      <c r="B5" s="447"/>
+      <c r="C5" s="447"/>
       <c r="D5" s="28" t="s">
         <v>1103</v>
       </c>
@@ -18565,9 +18600,9 @@
       <c r="N5" s="460"/>
     </row>
     <row r="6" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A6" s="437"/>
-      <c r="B6" s="437"/>
-      <c r="C6" s="437"/>
+      <c r="A6" s="447"/>
+      <c r="B6" s="447"/>
+      <c r="C6" s="447"/>
       <c r="D6" s="28" t="s">
         <v>1653</v>
       </c>
@@ -18586,16 +18621,16 @@
       <c r="N6" s="460"/>
     </row>
     <row r="7" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A7" s="437"/>
-      <c r="B7" s="437"/>
-      <c r="C7" s="437"/>
+      <c r="A7" s="447"/>
+      <c r="B7" s="447"/>
+      <c r="C7" s="447"/>
       <c r="D7" s="28" t="s">
-        <v>1021</v>
+        <v>1739</v>
       </c>
       <c r="E7" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="434"/>
+      <c r="F7" s="437"/>
       <c r="G7" s="434" t="s">
         <v>170</v>
       </c>
@@ -18607,36 +18642,36 @@
       <c r="N7" s="460"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="437"/>
-      <c r="B8" s="437" t="s">
-        <v>214</v>
-      </c>
-      <c r="C8" s="437" t="s">
-        <v>1102</v>
-      </c>
+      <c r="A8" s="447"/>
+      <c r="B8" s="448"/>
+      <c r="C8" s="448"/>
       <c r="D8" s="28" t="s">
-        <v>1117</v>
+        <v>1021</v>
       </c>
       <c r="E8" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="295"/>
+      <c r="F8" s="434"/>
       <c r="G8" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="H8" s="295"/>
-      <c r="I8" s="295"/>
-      <c r="J8" s="295"/>
-      <c r="K8" s="295"/>
+      <c r="H8" s="434"/>
+      <c r="I8" s="434"/>
+      <c r="J8" s="434"/>
+      <c r="K8" s="434"/>
       <c r="L8" s="459"/>
       <c r="N8" s="460"/>
     </row>
     <row r="9" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A9" s="437"/>
-      <c r="B9" s="437"/>
-      <c r="C9" s="437"/>
-      <c r="D9" s="295" t="s">
-        <v>1118</v>
+      <c r="A9" s="447"/>
+      <c r="B9" s="446" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="446" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>1117</v>
       </c>
       <c r="E9" s="434" t="s">
         <v>24</v>
@@ -18653,11 +18688,11 @@
       <c r="N9" s="460"/>
     </row>
     <row r="10" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A10" s="437"/>
-      <c r="B10" s="437"/>
-      <c r="C10" s="437"/>
+      <c r="A10" s="447"/>
+      <c r="B10" s="447"/>
+      <c r="C10" s="447"/>
       <c r="D10" s="295" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E10" s="434" t="s">
         <v>24</v>
@@ -18674,11 +18709,11 @@
       <c r="N10" s="460"/>
     </row>
     <row r="11" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A11" s="437"/>
-      <c r="B11" s="437"/>
-      <c r="C11" s="437"/>
+      <c r="A11" s="447"/>
+      <c r="B11" s="447"/>
+      <c r="C11" s="447"/>
       <c r="D11" s="295" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E11" s="434" t="s">
         <v>24</v>
@@ -18695,11 +18730,11 @@
       <c r="N11" s="460"/>
     </row>
     <row r="12" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A12" s="437"/>
-      <c r="B12" s="437"/>
-      <c r="C12" s="437"/>
+      <c r="A12" s="447"/>
+      <c r="B12" s="447"/>
+      <c r="C12" s="447"/>
       <c r="D12" s="295" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E12" s="434" t="s">
         <v>24</v>
@@ -18715,12 +18750,12 @@
       <c r="L12" s="459"/>
       <c r="N12" s="460"/>
     </row>
-    <row r="13" spans="1:14" ht="28.500000" customHeight="1">
-      <c r="A13" s="437"/>
-      <c r="B13" s="437"/>
-      <c r="C13" s="437"/>
+    <row r="13" spans="1:14">
+      <c r="A13" s="447"/>
+      <c r="B13" s="447"/>
+      <c r="C13" s="447"/>
       <c r="D13" s="295" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E13" s="434" t="s">
         <v>24</v>
@@ -18736,16 +18771,12 @@
       <c r="L13" s="459"/>
       <c r="N13" s="460"/>
     </row>
-    <row r="14" spans="1:14" ht="28.500000" customHeight="1">
-      <c r="A14" s="437"/>
-      <c r="B14" s="437" t="s">
-        <v>278</v>
-      </c>
-      <c r="C14" s="437" t="s">
-        <v>436</v>
-      </c>
+    <row r="14" spans="1:14">
+      <c r="A14" s="447"/>
+      <c r="B14" s="448"/>
+      <c r="C14" s="448"/>
       <c r="D14" s="295" t="s">
-        <v>1147</v>
+        <v>1122</v>
       </c>
       <c r="E14" s="434" t="s">
         <v>24</v>
@@ -18761,33 +18792,37 @@
       <c r="L14" s="459"/>
       <c r="N14" s="460"/>
     </row>
-    <row r="15" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A15" s="437"/>
-      <c r="B15" s="437"/>
-      <c r="C15" s="437"/>
+    <row r="15" spans="1:14" ht="28.500000" customHeight="1">
+      <c r="A15" s="447"/>
+      <c r="B15" s="446" t="s">
+        <v>278</v>
+      </c>
+      <c r="C15" s="446" t="s">
+        <v>436</v>
+      </c>
       <c r="D15" s="295" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="E15" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="434"/>
+      <c r="F15" s="295"/>
       <c r="G15" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="H15" s="434"/>
-      <c r="I15" s="434"/>
-      <c r="J15" s="434"/>
-      <c r="K15" s="434"/>
+      <c r="H15" s="295"/>
+      <c r="I15" s="295"/>
+      <c r="J15" s="295"/>
+      <c r="K15" s="295"/>
       <c r="L15" s="459"/>
       <c r="M15" s="459"/>
     </row>
     <row r="16" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A16" s="437"/>
-      <c r="B16" s="437"/>
-      <c r="C16" s="437"/>
+      <c r="A16" s="447"/>
+      <c r="B16" s="447"/>
+      <c r="C16" s="447"/>
       <c r="D16" s="295" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="E16" s="434" t="s">
         <v>24</v>
@@ -18805,11 +18840,11 @@
       <c r="N16" s="166"/>
     </row>
     <row r="17" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A17" s="437"/>
-      <c r="B17" s="437"/>
-      <c r="C17" s="437"/>
+      <c r="A17" s="447"/>
+      <c r="B17" s="447"/>
+      <c r="C17" s="447"/>
       <c r="D17" s="295" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="E17" s="434" t="s">
         <v>24</v>
@@ -18827,11 +18862,11 @@
       <c r="N17" s="166"/>
     </row>
     <row r="18" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A18" s="437"/>
-      <c r="B18" s="437"/>
-      <c r="C18" s="437"/>
+      <c r="A18" s="447"/>
+      <c r="B18" s="447"/>
+      <c r="C18" s="447"/>
       <c r="D18" s="295" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="E18" s="434" t="s">
         <v>24</v>
@@ -18849,11 +18884,11 @@
       <c r="N18" s="166"/>
     </row>
     <row r="19" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A19" s="437"/>
-      <c r="B19" s="437"/>
-      <c r="C19" s="437"/>
+      <c r="A19" s="447"/>
+      <c r="B19" s="447"/>
+      <c r="C19" s="447"/>
       <c r="D19" s="295" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="E19" s="434" t="s">
         <v>24</v>
@@ -18871,11 +18906,11 @@
       <c r="N19" s="166"/>
     </row>
     <row r="20" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A20" s="437"/>
-      <c r="B20" s="437"/>
-      <c r="C20" s="437"/>
+      <c r="A20" s="447"/>
+      <c r="B20" s="447"/>
+      <c r="C20" s="447"/>
       <c r="D20" s="295" t="s">
-        <v>1122</v>
+        <v>1145</v>
       </c>
       <c r="E20" s="434" t="s">
         <v>24</v>
@@ -18893,11 +18928,11 @@
       <c r="N20" s="166"/>
     </row>
     <row r="21" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A21" s="437"/>
-      <c r="B21" s="437"/>
-      <c r="C21" s="437"/>
+      <c r="A21" s="447"/>
+      <c r="B21" s="447"/>
+      <c r="C21" s="447"/>
       <c r="D21" s="295" t="s">
-        <v>804</v>
+        <v>1122</v>
       </c>
       <c r="E21" s="434" t="s">
         <v>24</v>
@@ -18915,15 +18950,11 @@
       <c r="N21" s="166"/>
     </row>
     <row r="22" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A22" s="437"/>
-      <c r="B22" s="437" t="s">
-        <v>279</v>
-      </c>
-      <c r="C22" s="437" t="s">
-        <v>1123</v>
-      </c>
+      <c r="A22" s="447"/>
+      <c r="B22" s="447"/>
+      <c r="C22" s="447"/>
       <c r="D22" s="295" t="s">
-        <v>350</v>
+        <v>804</v>
       </c>
       <c r="E22" s="434" t="s">
         <v>24</v>
@@ -18941,11 +18972,11 @@
       <c r="N22" s="166"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="437"/>
-      <c r="B23" s="437"/>
-      <c r="C23" s="437"/>
+      <c r="A23" s="447"/>
+      <c r="B23" s="448"/>
+      <c r="C23" s="448"/>
       <c r="D23" s="295" t="s">
-        <v>1124</v>
+        <v>350</v>
       </c>
       <c r="E23" s="434" t="s">
         <v>24</v>
@@ -18962,64 +18993,68 @@
       <c r="M23" s="166"/>
       <c r="N23" s="166"/>
     </row>
-    <row r="24" spans="1:14" ht="42.750000" customHeight="1">
-      <c r="A24" s="437"/>
+    <row r="24" spans="1:14" ht="28.500000" customHeight="1">
+      <c r="A24" s="447"/>
       <c r="B24" s="437" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C24" s="438" t="s">
-        <v>1152</v>
+        <v>1123</v>
       </c>
       <c r="D24" s="295" t="s">
-        <v>1654</v>
+        <v>1124</v>
       </c>
       <c r="E24" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="F24" s="434"/>
       <c r="G24" s="434" t="s">
         <v>170</v>
       </c>
       <c r="H24" s="434"/>
       <c r="I24" s="434"/>
       <c r="J24" s="434"/>
-      <c r="K24" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="K24" s="434"/>
       <c r="L24" s="459"/>
       <c r="M24" s="166"/>
       <c r="N24" s="166"/>
     </row>
-    <row r="25" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A25" s="437"/>
-      <c r="B25" s="437"/>
-      <c r="C25" s="438"/>
-      <c r="D25" s="28" t="s">
-        <v>1655</v>
+    <row r="25" spans="1:14" ht="42.750000" customHeight="1">
+      <c r="A25" s="447"/>
+      <c r="B25" s="446" t="s">
+        <v>284</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D25" s="295" t="s">
+        <v>1654</v>
       </c>
       <c r="E25" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="295"/>
+      <c r="F25" s="434" t="s">
+        <v>170</v>
+      </c>
       <c r="G25" s="434" t="s">
         <v>170</v>
       </c>
       <c r="H25" s="434"/>
       <c r="I25" s="434"/>
       <c r="J25" s="434"/>
-      <c r="K25" s="434"/>
+      <c r="K25" s="434" t="s">
+        <v>170</v>
+      </c>
       <c r="L25" s="459"/>
       <c r="M25" s="166"/>
       <c r="N25" s="166"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="437"/>
-      <c r="B26" s="437"/>
-      <c r="C26" s="438"/>
+      <c r="A26" s="447"/>
+      <c r="B26" s="447"/>
+      <c r="C26" s="106"/>
       <c r="D26" s="28" t="s">
-        <v>1662</v>
+        <v>1740</v>
       </c>
       <c r="E26" s="434" t="s">
         <v>24</v>
@@ -19036,12 +19071,12 @@
       <c r="M26" s="166"/>
       <c r="N26" s="166"/>
     </row>
-    <row r="27" spans="1:14" ht="99.750000" customHeight="1">
-      <c r="A27" s="437"/>
-      <c r="B27" s="437"/>
-      <c r="C27" s="438"/>
-      <c r="D27" s="30" t="s">
-        <v>1659</v>
+    <row r="27" spans="1:14">
+      <c r="A27" s="447"/>
+      <c r="B27" s="447"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="28" t="s">
+        <v>1662</v>
       </c>
       <c r="E27" s="434" t="s">
         <v>24</v>
@@ -19058,20 +19093,20 @@
       <c r="M27" s="166"/>
       <c r="N27" s="166"/>
     </row>
-    <row r="28" spans="1:14" ht="71.250000" customHeight="1">
-      <c r="A28" s="437"/>
-      <c r="B28" s="437"/>
-      <c r="C28" s="438"/>
-      <c r="D28" s="28" t="s">
-        <v>1672</v>
+    <row r="28" spans="1:14" ht="28.500000" customHeight="1">
+      <c r="A28" s="447"/>
+      <c r="B28" s="447"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="30" t="s">
+        <v>1743</v>
       </c>
       <c r="E28" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="434" t="s">
+      <c r="F28" s="295"/>
+      <c r="G28" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="G28" s="434"/>
       <c r="H28" s="434"/>
       <c r="I28" s="434"/>
       <c r="J28" s="434"/>
@@ -19080,12 +19115,12 @@
       <c r="M28" s="166"/>
       <c r="N28" s="166"/>
     </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="437"/>
-      <c r="B29" s="437"/>
-      <c r="C29" s="438"/>
-      <c r="D29" s="295" t="s">
-        <v>1663</v>
+    <row r="29" spans="1:14" ht="57.000000" customHeight="1">
+      <c r="A29" s="447"/>
+      <c r="B29" s="447"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="28" t="s">
+        <v>1672</v>
       </c>
       <c r="E29" s="434" t="s">
         <v>24</v>
@@ -19103,11 +19138,11 @@
       <c r="N29" s="166"/>
     </row>
     <row r="30" spans="1:14" ht="28.500000" customHeight="1">
-      <c r="A30" s="437"/>
-      <c r="B30" s="437"/>
-      <c r="C30" s="438"/>
+      <c r="A30" s="447"/>
+      <c r="B30" s="447"/>
+      <c r="C30" s="106"/>
       <c r="D30" s="295" t="s">
-        <v>1670</v>
+        <v>1663</v>
       </c>
       <c r="E30" s="434" t="s">
         <v>24</v>
@@ -19115,9 +19150,7 @@
       <c r="F30" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="G30" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="G30" s="434"/>
       <c r="H30" s="434"/>
       <c r="I30" s="434"/>
       <c r="J30" s="434"/>
@@ -19126,12 +19159,12 @@
       <c r="M30" s="166"/>
       <c r="N30" s="166"/>
     </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="437"/>
-      <c r="B31" s="437"/>
-      <c r="C31" s="438"/>
+    <row r="31" spans="1:14" ht="28.500000" customHeight="1">
+      <c r="A31" s="447"/>
+      <c r="B31" s="447"/>
+      <c r="C31" s="106"/>
       <c r="D31" s="295" t="s">
-        <v>1201</v>
+        <v>1744</v>
       </c>
       <c r="E31" s="434" t="s">
         <v>24</v>
@@ -19150,12 +19183,12 @@
       <c r="M31" s="166"/>
       <c r="N31" s="166"/>
     </row>
-    <row r="32" spans="1:14" ht="28.500000" customHeight="1">
-      <c r="A32" s="437"/>
-      <c r="B32" s="437"/>
-      <c r="C32" s="438"/>
+    <row r="32" spans="1:14">
+      <c r="A32" s="447"/>
+      <c r="B32" s="447"/>
+      <c r="C32" s="106"/>
       <c r="D32" s="295" t="s">
-        <v>1168</v>
+        <v>1201</v>
       </c>
       <c r="E32" s="434" t="s">
         <v>24</v>
@@ -19174,12 +19207,12 @@
       <c r="M32" s="166"/>
       <c r="N32" s="166"/>
     </row>
-    <row r="33" spans="1:14" ht="28.500000" customHeight="1">
-      <c r="A33" s="437"/>
-      <c r="B33" s="437"/>
-      <c r="C33" s="437"/>
+    <row r="33" spans="1:16384" ht="28.500000" customHeight="1">
+      <c r="A33" s="447"/>
+      <c r="B33" s="448"/>
+      <c r="C33" s="448"/>
       <c r="D33" s="295" t="s">
-        <v>1277</v>
+        <v>1745</v>
       </c>
       <c r="E33" s="434" t="s">
         <v>24</v>
@@ -19190,20 +19223,20 @@
       <c r="G33" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="H33" s="295"/>
-      <c r="I33" s="295"/>
-      <c r="J33" s="295"/>
-      <c r="K33" s="295"/>
+      <c r="H33" s="434"/>
+      <c r="I33" s="434"/>
+      <c r="J33" s="434"/>
+      <c r="K33" s="434"/>
       <c r="L33" s="311"/>
       <c r="M33" s="166"/>
       <c r="N33" s="166"/>
     </row>
-    <row r="34" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A34" s="437"/>
-      <c r="B34" s="437" t="s">
+    <row r="34" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A34" s="447"/>
+      <c r="B34" s="446" t="s">
         <v>291</v>
       </c>
-      <c r="C34" s="438" t="s">
+      <c r="C34" s="105" t="s">
         <v>151</v>
       </c>
       <c r="D34" s="295" t="s">
@@ -19224,10 +19257,10 @@
       <c r="M34" s="166"/>
       <c r="N34" s="166"/>
     </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="437"/>
-      <c r="B35" s="437"/>
-      <c r="C35" s="437"/>
+    <row r="35" spans="1:16384">
+      <c r="A35" s="447"/>
+      <c r="B35" s="447"/>
+      <c r="C35" s="106"/>
       <c r="D35" s="295" t="s">
         <v>1203</v>
       </c>
@@ -19246,10 +19279,10 @@
       <c r="M35" s="166"/>
       <c r="N35" s="166"/>
     </row>
-    <row r="36" spans="1:14" ht="228.000000">
-      <c r="A36" s="437"/>
-      <c r="B36" s="437"/>
-      <c r="C36" s="438"/>
+    <row r="36" spans="1:16384" ht="99.750000" customHeight="1">
+      <c r="A36" s="447"/>
+      <c r="B36" s="448"/>
+      <c r="C36" s="111"/>
       <c r="D36" s="295" t="s">
         <v>1738</v>
       </c>
@@ -19268,12 +19301,16 @@
       <c r="M36" s="166"/>
       <c r="N36" s="166"/>
     </row>
-    <row r="37" spans="1:14" ht="28.500000">
-      <c r="A37" s="437"/>
-      <c r="B37" s="437"/>
-      <c r="C37" s="438"/>
+    <row r="37" spans="1:16384">
+      <c r="A37" s="447"/>
+      <c r="B37" s="437" t="s">
+        <v>292</v>
+      </c>
+      <c r="C37" s="438" t="s">
+        <v>824</v>
+      </c>
       <c r="D37" s="295" t="s">
-        <v>1277</v>
+        <v>1227</v>
       </c>
       <c r="E37" s="434" t="s">
         <v>24</v>
@@ -19286,20 +19323,22 @@
       <c r="I37" s="434"/>
       <c r="J37" s="434"/>
       <c r="K37" s="434"/>
-      <c r="L37" s="459"/>
-      <c r="M37" s="166"/>
-      <c r="N37" s="166"/>
-    </row>
-    <row r="38" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A38" s="437"/>
-      <c r="B38" s="437" t="s">
-        <v>292</v>
-      </c>
-      <c r="C38" s="438" t="s">
-        <v>824</v>
-      </c>
+      <c r="N37" s="460"/>
+      <c r="XEW37" s="0"/>
+      <c r="XEX37" s="0"/>
+      <c r="XEY37" s="0"/>
+      <c r="XEZ37" s="0"/>
+      <c r="XFA37" s="0"/>
+      <c r="XFB37" s="0"/>
+      <c r="XFC37" s="0"/>
+      <c r="XFD37" s="0"/>
+    </row>
+    <row r="38" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A38" s="447"/>
+      <c r="B38" s="437"/>
+      <c r="C38" s="438"/>
       <c r="D38" s="295" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="E38" s="434" t="s">
         <v>24</v>
@@ -19316,12 +19355,12 @@
       <c r="M38" s="166"/>
       <c r="N38" s="166"/>
     </row>
-    <row r="39" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A39" s="437"/>
+    <row r="39" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A39" s="447"/>
       <c r="B39" s="437"/>
       <c r="C39" s="438"/>
       <c r="D39" s="295" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E39" s="434" t="s">
         <v>24</v>
@@ -19338,12 +19377,12 @@
       <c r="M39" s="166"/>
       <c r="N39" s="166"/>
     </row>
-    <row r="40" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A40" s="437"/>
+    <row r="40" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A40" s="447"/>
       <c r="B40" s="437"/>
       <c r="C40" s="438"/>
-      <c r="D40" s="295" t="s">
-        <v>1242</v>
+      <c r="D40" s="28" t="s">
+        <v>1243</v>
       </c>
       <c r="E40" s="434" t="s">
         <v>24</v>
@@ -19360,12 +19399,12 @@
       <c r="M40" s="166"/>
       <c r="N40" s="166"/>
     </row>
-    <row r="41" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A41" s="437"/>
+    <row r="41" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A41" s="447"/>
       <c r="B41" s="437"/>
       <c r="C41" s="438"/>
       <c r="D41" s="28" t="s">
-        <v>1243</v>
+        <v>1150</v>
       </c>
       <c r="E41" s="434" t="s">
         <v>24</v>
@@ -19382,12 +19421,12 @@
       <c r="M41" s="166"/>
       <c r="N41" s="166"/>
     </row>
-    <row r="42" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A42" s="437"/>
+    <row r="42" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A42" s="447"/>
       <c r="B42" s="437"/>
       <c r="C42" s="438"/>
       <c r="D42" s="28" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E42" s="434" t="s">
         <v>24</v>
@@ -19404,12 +19443,12 @@
       <c r="M42" s="166"/>
       <c r="N42" s="166"/>
     </row>
-    <row r="43" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A43" s="437"/>
+    <row r="43" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A43" s="447"/>
       <c r="B43" s="437"/>
       <c r="C43" s="438"/>
       <c r="D43" s="28" t="s">
-        <v>1151</v>
+        <v>1245</v>
       </c>
       <c r="E43" s="434" t="s">
         <v>24</v>
@@ -19426,12 +19465,12 @@
       <c r="M43" s="166"/>
       <c r="N43" s="166"/>
     </row>
-    <row r="44" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A44" s="437"/>
+    <row r="44" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A44" s="447"/>
       <c r="B44" s="437"/>
       <c r="C44" s="438"/>
       <c r="D44" s="28" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="E44" s="434" t="s">
         <v>24</v>
@@ -19448,12 +19487,12 @@
       <c r="M44" s="166"/>
       <c r="N44" s="166"/>
     </row>
-    <row r="45" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A45" s="437"/>
+    <row r="45" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A45" s="447"/>
       <c r="B45" s="437"/>
       <c r="C45" s="438"/>
       <c r="D45" s="28" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="E45" s="434" t="s">
         <v>24</v>
@@ -19470,12 +19509,12 @@
       <c r="M45" s="166"/>
       <c r="N45" s="166"/>
     </row>
-    <row r="46" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A46" s="437"/>
+    <row r="46" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A46" s="447"/>
       <c r="B46" s="437"/>
       <c r="C46" s="438"/>
       <c r="D46" s="28" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="E46" s="434" t="s">
         <v>24</v>
@@ -19492,12 +19531,12 @@
       <c r="M46" s="166"/>
       <c r="N46" s="166"/>
     </row>
-    <row r="47" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A47" s="437"/>
+    <row r="47" spans="1:16384" ht="17.250000" customHeight="1">
+      <c r="A47" s="447"/>
       <c r="B47" s="437"/>
       <c r="C47" s="438"/>
-      <c r="D47" s="28" t="s">
-        <v>1248</v>
+      <c r="D47" s="295" t="s">
+        <v>1250</v>
       </c>
       <c r="E47" s="434" t="s">
         <v>24</v>
@@ -19514,12 +19553,12 @@
       <c r="M47" s="166"/>
       <c r="N47" s="166"/>
     </row>
-    <row r="48" spans="1:14" ht="17.250000" customHeight="1">
-      <c r="A48" s="437"/>
+    <row r="48" spans="1:16384" ht="57.000000" customHeight="1">
+      <c r="A48" s="447"/>
       <c r="B48" s="437"/>
       <c r="C48" s="438"/>
-      <c r="D48" s="295" t="s">
-        <v>1250</v>
+      <c r="D48" s="28" t="s">
+        <v>1252</v>
       </c>
       <c r="E48" s="434" t="s">
         <v>24</v>
@@ -19536,12 +19575,16 @@
       <c r="M48" s="166"/>
       <c r="N48" s="166"/>
     </row>
-    <row r="49" spans="1:20" ht="57.000000">
-      <c r="A49" s="437"/>
-      <c r="B49" s="437"/>
-      <c r="C49" s="438"/>
+    <row r="49" spans="1:20">
+      <c r="A49" s="447"/>
+      <c r="B49" s="437" t="s">
+        <v>301</v>
+      </c>
+      <c r="C49" s="438" t="s">
+        <v>1261</v>
+      </c>
       <c r="D49" s="28" t="s">
-        <v>1252</v>
+        <v>1202</v>
       </c>
       <c r="E49" s="434" t="s">
         <v>24</v>
@@ -19558,79 +19601,75 @@
       <c r="M49" s="166"/>
       <c r="N49" s="166"/>
     </row>
-    <row r="50" spans="1:20">
-      <c r="A50" s="437"/>
-      <c r="B50" s="437" t="s">
-        <v>301</v>
-      </c>
-      <c r="C50" s="438" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>1202</v>
-      </c>
-      <c r="E50" s="434" t="s">
+    <row r="50" spans="1:20" ht="384.750000" customHeight="1">
+      <c r="A50" s="447"/>
+      <c r="B50" s="437"/>
+      <c r="C50" s="438"/>
+      <c r="D50" s="661" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E50" s="472" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="434" t="s">
+      <c r="F50" s="472" t="s">
         <v>170</v>
       </c>
-      <c r="G50" s="434"/>
-      <c r="H50" s="434"/>
-      <c r="I50" s="434"/>
-      <c r="J50" s="434"/>
-      <c r="K50" s="434"/>
-    </row>
-    <row r="51" spans="1:20" ht="319.800000" customHeight="1">
-      <c r="A51" s="437"/>
+      <c r="G50" s="472"/>
+      <c r="H50" s="472"/>
+      <c r="I50" s="472"/>
+      <c r="J50" s="472"/>
+      <c r="K50" s="472"/>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="A51" s="448"/>
       <c r="B51" s="437"/>
       <c r="C51" s="438"/>
-      <c r="D51" s="659" t="s">
-        <v>1719</v>
-      </c>
-      <c r="E51" s="434" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="434" t="s">
-        <v>170</v>
-      </c>
-      <c r="G51" s="434"/>
-      <c r="H51" s="434"/>
-      <c r="I51" s="434"/>
-      <c r="J51" s="434"/>
-      <c r="K51" s="434"/>
+      <c r="D51" s="663"/>
+      <c r="E51" s="474"/>
+      <c r="F51" s="474"/>
+      <c r="G51" s="474"/>
+      <c r="H51" s="474"/>
+      <c r="I51" s="474"/>
+      <c r="J51" s="474"/>
+      <c r="K51" s="474"/>
     </row>
     <row r="52" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A52" s="437"/>
-      <c r="B52" s="437"/>
-      <c r="C52" s="438"/>
-      <c r="D52" s="296" t="s">
-        <v>1277</v>
+      <c r="A52" s="86" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B52" s="437" t="s">
+        <v>331</v>
+      </c>
+      <c r="C52" s="438" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D52" s="295" t="s">
+        <v>1202</v>
       </c>
       <c r="E52" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="434" t="s">
+      <c r="F52" s="437" t="s">
         <v>170</v>
       </c>
       <c r="G52" s="434"/>
-      <c r="H52" s="434"/>
-      <c r="I52" s="434"/>
-      <c r="J52" s="434"/>
+      <c r="H52" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="J52" s="434" t="s">
+        <v>170</v>
+      </c>
       <c r="K52" s="434"/>
     </row>
     <row r="53" spans="1:20" ht="28.500000" customHeight="1">
-      <c r="A53" s="437" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B53" s="437" t="s">
-        <v>331</v>
-      </c>
-      <c r="C53" s="438" t="s">
-        <v>1693</v>
-      </c>
-      <c r="D53" s="295" t="s">
-        <v>1202</v>
+      <c r="A53" s="86"/>
+      <c r="B53" s="437"/>
+      <c r="C53" s="437"/>
+      <c r="D53" s="505" t="s">
+        <v>1713</v>
       </c>
       <c r="E53" s="434" t="s">
         <v>24</v>
@@ -19648,35 +19687,23 @@
       <c r="J53" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="K53" s="434"/>
+      <c r="K53" s="437"/>
     </row>
     <row r="54" spans="1:20">
-      <c r="A54" s="437"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="437"/>
       <c r="C54" s="437"/>
-      <c r="D54" s="505" t="s">
-        <v>1713</v>
-      </c>
-      <c r="E54" s="434" t="s">
-        <v>24</v>
-      </c>
-      <c r="F54" s="437" t="s">
-        <v>170</v>
-      </c>
+      <c r="D54" s="505"/>
+      <c r="E54" s="434"/>
+      <c r="F54" s="437"/>
       <c r="G54" s="434"/>
-      <c r="H54" s="434" t="s">
-        <v>170</v>
-      </c>
-      <c r="I54" s="434" t="s">
-        <v>170</v>
-      </c>
-      <c r="J54" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="H54" s="434"/>
+      <c r="I54" s="434"/>
+      <c r="J54" s="434"/>
       <c r="K54" s="437"/>
     </row>
     <row r="55" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A55" s="437"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="437"/>
       <c r="C55" s="437"/>
       <c r="D55" s="505"/>
@@ -19689,7 +19716,7 @@
       <c r="K55" s="437"/>
     </row>
     <row r="56" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A56" s="437"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="437"/>
       <c r="C56" s="437"/>
       <c r="D56" s="505"/>
@@ -19710,7 +19737,7 @@
       <c r="T56" s="463"/>
     </row>
     <row r="57" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A57" s="437"/>
+      <c r="A57" s="86"/>
       <c r="B57" s="437"/>
       <c r="C57" s="437"/>
       <c r="D57" s="505"/>
@@ -19731,7 +19758,7 @@
       <c r="T57" s="463"/>
     </row>
     <row r="58" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A58" s="437"/>
+      <c r="A58" s="86"/>
       <c r="B58" s="437"/>
       <c r="C58" s="437"/>
       <c r="D58" s="505"/>
@@ -19752,7 +19779,7 @@
       <c r="T58" s="463"/>
     </row>
     <row r="59" spans="1:20">
-      <c r="A59" s="437"/>
+      <c r="A59" s="86"/>
       <c r="B59" s="437"/>
       <c r="C59" s="437"/>
       <c r="D59" s="505"/>
@@ -19772,18 +19799,24 @@
       <c r="S59" s="463"/>
       <c r="T59" s="463"/>
     </row>
-    <row r="60" spans="1:20" ht="408.600000" customHeight="1">
-      <c r="A60" s="437"/>
+    <row r="60" spans="1:20">
+      <c r="A60" s="86"/>
       <c r="B60" s="437"/>
       <c r="C60" s="437"/>
-      <c r="D60" s="505"/>
-      <c r="E60" s="434"/>
-      <c r="F60" s="437"/>
-      <c r="G60" s="434"/>
-      <c r="H60" s="434"/>
-      <c r="I60" s="434"/>
-      <c r="J60" s="434"/>
-      <c r="K60" s="437"/>
+      <c r="D60" s="295" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E60" s="434" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="295"/>
+      <c r="H60" s="295"/>
+      <c r="I60" s="295"/>
+      <c r="J60" s="295"/>
+      <c r="K60" s="296"/>
       <c r="M60" s="311"/>
       <c r="N60" s="463"/>
       <c r="O60" s="463"/>
@@ -19794,11 +19827,15 @@
       <c r="T60" s="463"/>
     </row>
     <row r="61" spans="1:20">
-      <c r="A61" s="437"/>
-      <c r="B61" s="437"/>
-      <c r="C61" s="437"/>
+      <c r="A61" s="86"/>
+      <c r="B61" s="437" t="s">
+        <v>332</v>
+      </c>
+      <c r="C61" s="437" t="s">
+        <v>1699</v>
+      </c>
       <c r="D61" s="295" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="E61" s="434" t="s">
         <v>24</v>
@@ -19807,10 +19844,14 @@
         <v>170</v>
       </c>
       <c r="G61" s="295"/>
-      <c r="H61" s="295"/>
-      <c r="I61" s="295"/>
-      <c r="J61" s="295"/>
-      <c r="K61" s="296"/>
+      <c r="H61" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="I61" s="434" t="s">
+        <v>170</v>
+      </c>
+      <c r="J61" s="434"/>
+      <c r="K61" s="295"/>
       <c r="M61" s="311"/>
       <c r="N61" s="463"/>
       <c r="O61" s="463"/>
@@ -19821,15 +19862,11 @@
       <c r="T61" s="463"/>
     </row>
     <row r="62" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A62" s="437"/>
-      <c r="B62" s="437" t="s">
-        <v>332</v>
-      </c>
-      <c r="C62" s="437" t="s">
-        <v>1699</v>
-      </c>
+      <c r="A62" s="86"/>
+      <c r="B62" s="437"/>
+      <c r="C62" s="437"/>
       <c r="D62" s="295" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="E62" s="434" t="s">
         <v>24</v>
@@ -19844,7 +19881,7 @@
       <c r="I62" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="J62" s="434"/>
+      <c r="J62" s="295"/>
       <c r="K62" s="295"/>
       <c r="M62" s="311"/>
       <c r="N62" s="463"/>
@@ -19855,12 +19892,12 @@
       <c r="S62" s="463"/>
       <c r="T62" s="463"/>
     </row>
-    <row r="63" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A63" s="437"/>
+    <row r="63" spans="1:20">
+      <c r="A63" s="86"/>
       <c r="B63" s="437"/>
       <c r="C63" s="437"/>
       <c r="D63" s="295" t="s">
-        <v>1701</v>
+        <v>1729</v>
       </c>
       <c r="E63" s="434" t="s">
         <v>24</v>
@@ -19887,12 +19924,12 @@
       <c r="S63" s="463"/>
       <c r="T63" s="463"/>
     </row>
-    <row r="64" spans="1:20" ht="28.500000">
-      <c r="A64" s="437"/>
+    <row r="64" spans="1:20">
+      <c r="A64" s="86"/>
       <c r="B64" s="437"/>
       <c r="C64" s="437"/>
       <c r="D64" s="295" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="E64" s="434" t="s">
         <v>24</v>
@@ -19920,11 +19957,11 @@
       <c r="T64" s="463"/>
     </row>
     <row r="65" spans="1:20">
-      <c r="A65" s="437"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="437"/>
       <c r="C65" s="437"/>
       <c r="D65" s="295" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="E65" s="434" t="s">
         <v>24</v>
@@ -19952,11 +19989,11 @@
       <c r="T65" s="463"/>
     </row>
     <row r="66" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A66" s="437"/>
+      <c r="A66" s="86"/>
       <c r="B66" s="437"/>
       <c r="C66" s="437"/>
       <c r="D66" s="295" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="E66" s="434" t="s">
         <v>24</v>
@@ -19984,11 +20021,11 @@
       <c r="T66" s="463"/>
     </row>
     <row r="67" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A67" s="437"/>
+      <c r="A67" s="86"/>
       <c r="B67" s="437"/>
       <c r="C67" s="437"/>
       <c r="D67" s="295" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="E67" s="434" t="s">
         <v>24</v>
@@ -20015,12 +20052,12 @@
       <c r="S67" s="463"/>
       <c r="T67" s="463"/>
     </row>
-    <row r="68" spans="1:20">
-      <c r="A68" s="437"/>
+    <row r="68" spans="1:20" ht="28.500000">
+      <c r="A68" s="86"/>
       <c r="B68" s="437"/>
       <c r="C68" s="437"/>
       <c r="D68" s="295" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="E68" s="434" t="s">
         <v>24</v>
@@ -20047,12 +20084,12 @@
       <c r="S68" s="463"/>
       <c r="T68" s="463"/>
     </row>
-    <row r="69" spans="1:20" ht="28.500000">
-      <c r="A69" s="437"/>
+    <row r="69" spans="1:20">
+      <c r="A69" s="86"/>
       <c r="B69" s="437"/>
       <c r="C69" s="437"/>
       <c r="D69" s="295" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="E69" s="434" t="s">
         <v>24</v>
@@ -20080,11 +20117,11 @@
       <c r="T69" s="463"/>
     </row>
     <row r="70" spans="1:20">
-      <c r="A70" s="437"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="437"/>
       <c r="C70" s="437"/>
       <c r="D70" s="295" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="E70" s="434" t="s">
         <v>24</v>
@@ -20112,11 +20149,11 @@
       <c r="T70" s="463"/>
     </row>
     <row r="71" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A71" s="437"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="437"/>
       <c r="C71" s="437"/>
       <c r="D71" s="295" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="E71" s="434" t="s">
         <v>24</v>
@@ -20144,11 +20181,11 @@
       <c r="T71" s="463"/>
     </row>
     <row r="72" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A72" s="437"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="437"/>
       <c r="C72" s="437"/>
       <c r="D72" s="295" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="E72" s="434" t="s">
         <v>24</v>
@@ -20156,15 +20193,15 @@
       <c r="F72" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="G72" s="295"/>
+      <c r="G72" s="434"/>
       <c r="H72" s="434" t="s">
         <v>170</v>
       </c>
       <c r="I72" s="434" t="s">
         <v>170</v>
       </c>
-      <c r="J72" s="295"/>
-      <c r="K72" s="295"/>
+      <c r="J72" s="434"/>
+      <c r="K72" s="434"/>
       <c r="L72" s="464"/>
       <c r="M72" s="311"/>
       <c r="N72" s="463"/>
@@ -20175,12 +20212,18 @@
       <c r="S72" s="463"/>
       <c r="T72" s="463"/>
     </row>
-    <row r="73" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A73" s="437"/>
-      <c r="B73" s="437"/>
-      <c r="C73" s="437"/>
-      <c r="D73" s="295" t="s">
-        <v>1711</v>
+    <row r="73" spans="1:20" ht="28.500000">
+      <c r="A73" s="437" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B73" s="434" t="s">
+        <v>336</v>
+      </c>
+      <c r="C73" s="438" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D73" s="103" t="s">
+        <v>1091</v>
       </c>
       <c r="E73" s="434" t="s">
         <v>24</v>
@@ -20207,18 +20250,12 @@
       <c r="S73" s="311"/>
       <c r="T73" s="463"/>
     </row>
-    <row r="74" spans="1:20" ht="28.500000" customHeight="1">
-      <c r="A74" s="437" t="s">
-        <v>1429</v>
-      </c>
-      <c r="B74" s="434" t="s">
-        <v>336</v>
-      </c>
-      <c r="C74" s="438" t="s">
-        <v>1092</v>
-      </c>
+    <row r="74" spans="1:20">
+      <c r="A74" s="437"/>
+      <c r="B74" s="434"/>
+      <c r="C74" s="438"/>
       <c r="D74" s="103" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="E74" s="434" t="s">
         <v>24</v>
@@ -20227,22 +20264,18 @@
         <v>170</v>
       </c>
       <c r="G74" s="434"/>
-      <c r="H74" s="434" t="s">
-        <v>170</v>
-      </c>
-      <c r="I74" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="H74" s="434"/>
+      <c r="I74" s="434"/>
       <c r="J74" s="434"/>
       <c r="K74" s="434"/>
       <c r="M74" s="459"/>
     </row>
-    <row r="75" spans="1:20" ht="28.500000" customHeight="1">
+    <row r="75" spans="1:20">
       <c r="A75" s="437"/>
       <c r="B75" s="434"/>
       <c r="C75" s="438"/>
       <c r="D75" s="103" t="s">
-        <v>1095</v>
+        <v>350</v>
       </c>
       <c r="E75" s="434" t="s">
         <v>24</v>
@@ -20258,37 +20291,37 @@
       <c r="M75" s="459"/>
     </row>
     <row r="76" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A76" s="437"/>
-      <c r="B76" s="434"/>
-      <c r="C76" s="438"/>
-      <c r="D76" s="103" t="s">
-        <v>350</v>
+      <c r="A76" s="437" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B76" s="434" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C76" s="434" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D76" s="295" t="s">
+        <v>934</v>
       </c>
       <c r="E76" s="434" t="s">
         <v>24</v>
       </c>
-      <c r="F76" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="F76" s="434"/>
       <c r="G76" s="434"/>
       <c r="H76" s="434"/>
       <c r="I76" s="434"/>
       <c r="J76" s="434"/>
-      <c r="K76" s="434"/>
+      <c r="K76" s="434" t="s">
+        <v>170</v>
+      </c>
       <c r="M76" s="459"/>
     </row>
     <row r="77" spans="1:20" ht="17.250000" customHeight="1">
-      <c r="A77" s="437" t="s">
-        <v>1430</v>
-      </c>
-      <c r="B77" s="434" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C77" s="434" t="s">
-        <v>1432</v>
-      </c>
+      <c r="A77" s="437"/>
+      <c r="B77" s="434"/>
+      <c r="C77" s="434"/>
       <c r="D77" s="295" t="s">
-        <v>934</v>
+        <v>749</v>
       </c>
       <c r="E77" s="434" t="s">
         <v>24</v>
@@ -20308,7 +20341,7 @@
       <c r="B78" s="434"/>
       <c r="C78" s="434"/>
       <c r="D78" s="295" t="s">
-        <v>749</v>
+        <v>935</v>
       </c>
       <c r="E78" s="434" t="s">
         <v>24</v>
@@ -20328,7 +20361,7 @@
       <c r="B79" s="434"/>
       <c r="C79" s="434"/>
       <c r="D79" s="295" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E79" s="434" t="s">
         <v>24</v>
@@ -20345,10 +20378,14 @@
     </row>
     <row r="80" spans="1:20" ht="17.250000" customHeight="1">
       <c r="A80" s="437"/>
-      <c r="B80" s="434"/>
-      <c r="C80" s="434"/>
+      <c r="B80" s="434" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C80" s="434" t="s">
+        <v>1425</v>
+      </c>
       <c r="D80" s="295" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E80" s="434" t="s">
         <v>24</v>
@@ -20365,14 +20402,10 @@
     </row>
     <row r="81" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A81" s="437"/>
-      <c r="B81" s="434" t="s">
-        <v>1424</v>
-      </c>
-      <c r="C81" s="434" t="s">
-        <v>1425</v>
-      </c>
+      <c r="B81" s="434"/>
+      <c r="C81" s="434"/>
       <c r="D81" s="295" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E81" s="434" t="s">
         <v>24</v>
@@ -20392,7 +20425,7 @@
       <c r="B82" s="434"/>
       <c r="C82" s="434"/>
       <c r="D82" s="295" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E82" s="434" t="s">
         <v>24</v>
@@ -20412,7 +20445,7 @@
       <c r="B83" s="434"/>
       <c r="C83" s="434"/>
       <c r="D83" s="295" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E83" s="434" t="s">
         <v>24</v>
@@ -20432,7 +20465,7 @@
       <c r="B84" s="434"/>
       <c r="C84" s="434"/>
       <c r="D84" s="295" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="E84" s="434" t="s">
         <v>24</v>
@@ -20452,7 +20485,7 @@
       <c r="B85" s="434"/>
       <c r="C85" s="434"/>
       <c r="D85" s="295" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E85" s="434" t="s">
         <v>24</v>
@@ -20472,7 +20505,7 @@
       <c r="B86" s="434"/>
       <c r="C86" s="434"/>
       <c r="D86" s="295" t="s">
-        <v>942</v>
+        <v>801</v>
       </c>
       <c r="E86" s="434" t="s">
         <v>24</v>
@@ -20492,7 +20525,7 @@
       <c r="B87" s="434"/>
       <c r="C87" s="434"/>
       <c r="D87" s="295" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E87" s="434" t="s">
         <v>24</v>
@@ -20512,7 +20545,7 @@
       <c r="B88" s="434"/>
       <c r="C88" s="434"/>
       <c r="D88" s="295" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E88" s="434" t="s">
         <v>24</v>
@@ -20532,7 +20565,7 @@
       <c r="B89" s="434"/>
       <c r="C89" s="434"/>
       <c r="D89" s="295" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E89" s="434" t="s">
         <v>24</v>
@@ -20552,7 +20585,7 @@
       <c r="B90" s="434"/>
       <c r="C90" s="434"/>
       <c r="D90" s="295" t="s">
-        <v>806</v>
+        <v>1000</v>
       </c>
       <c r="E90" s="434" t="s">
         <v>24</v>
@@ -20569,10 +20602,14 @@
     </row>
     <row r="91" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A91" s="437"/>
-      <c r="B91" s="434"/>
-      <c r="C91" s="434"/>
+      <c r="B91" s="437" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C91" s="437" t="s">
+        <v>1435</v>
+      </c>
       <c r="D91" s="295" t="s">
-        <v>1000</v>
+        <v>814</v>
       </c>
       <c r="E91" s="434" t="s">
         <v>24</v>
@@ -20589,14 +20626,10 @@
     </row>
     <row r="92" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A92" s="437"/>
-      <c r="B92" s="437" t="s">
-        <v>1720</v>
-      </c>
-      <c r="C92" s="437" t="s">
-        <v>1435</v>
-      </c>
+      <c r="B92" s="437"/>
+      <c r="C92" s="437"/>
       <c r="D92" s="295" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="E92" s="434" t="s">
         <v>24</v>
@@ -20616,7 +20649,7 @@
       <c r="B93" s="437"/>
       <c r="C93" s="437"/>
       <c r="D93" s="295" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E93" s="434" t="s">
         <v>24</v>
@@ -20636,7 +20669,7 @@
       <c r="B94" s="437"/>
       <c r="C94" s="437"/>
       <c r="D94" s="295" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="E94" s="434" t="s">
         <v>24</v>
@@ -20657,7 +20690,7 @@
       <c r="B95" s="437"/>
       <c r="C95" s="437"/>
       <c r="D95" s="295" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="E95" s="434" t="s">
         <v>24</v>
@@ -20678,7 +20711,7 @@
       <c r="B96" s="437"/>
       <c r="C96" s="437"/>
       <c r="D96" s="295" t="s">
-        <v>816</v>
+        <v>976</v>
       </c>
       <c r="E96" s="434" t="s">
         <v>24</v>
@@ -20699,7 +20732,7 @@
       <c r="B97" s="437"/>
       <c r="C97" s="437"/>
       <c r="D97" s="295" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E97" s="434" t="s">
         <v>24</v>
@@ -20717,10 +20750,14 @@
     </row>
     <row r="98" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A98" s="437"/>
-      <c r="B98" s="437"/>
-      <c r="C98" s="437"/>
+      <c r="B98" s="437" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C98" s="437" t="s">
+        <v>1714</v>
+      </c>
       <c r="D98" s="295" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E98" s="434" t="s">
         <v>24</v>
@@ -20738,14 +20775,10 @@
     </row>
     <row r="99" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A99" s="437"/>
-      <c r="B99" s="437" t="s">
-        <v>1721</v>
-      </c>
-      <c r="C99" s="437" t="s">
-        <v>1714</v>
-      </c>
+      <c r="B99" s="437"/>
+      <c r="C99" s="437"/>
       <c r="D99" s="295" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="E99" s="434" t="s">
         <v>24</v>
@@ -20764,7 +20797,7 @@
       <c r="B100" s="437"/>
       <c r="C100" s="437"/>
       <c r="D100" s="295" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E100" s="434" t="s">
         <v>24</v>
@@ -20783,7 +20816,7 @@
       <c r="B101" s="437"/>
       <c r="C101" s="437"/>
       <c r="D101" s="295" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E101" s="434" t="s">
         <v>24</v>
@@ -20802,7 +20835,7 @@
       <c r="B102" s="437"/>
       <c r="C102" s="437"/>
       <c r="D102" s="295" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="E102" s="434" t="s">
         <v>24</v>
@@ -20821,7 +20854,7 @@
       <c r="B103" s="437"/>
       <c r="C103" s="437"/>
       <c r="D103" s="295" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E103" s="434" t="s">
         <v>24</v>
@@ -20840,7 +20873,7 @@
       <c r="B104" s="437"/>
       <c r="C104" s="437"/>
       <c r="D104" s="295" t="s">
-        <v>978</v>
+        <v>1715</v>
       </c>
       <c r="E104" s="434" t="s">
         <v>24</v>
@@ -20856,10 +20889,14 @@
     </row>
     <row r="105" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A105" s="437"/>
-      <c r="B105" s="437"/>
-      <c r="C105" s="437"/>
+      <c r="B105" s="437" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C105" s="437" t="s">
+        <v>1699</v>
+      </c>
       <c r="D105" s="295" t="s">
-        <v>1715</v>
+        <v>1726</v>
       </c>
       <c r="E105" s="434" t="s">
         <v>24</v>
@@ -20875,14 +20912,10 @@
     </row>
     <row r="106" spans="1:13" ht="17.250000" customHeight="1">
       <c r="A106" s="437"/>
-      <c r="B106" s="437" t="s">
-        <v>1722</v>
-      </c>
-      <c r="C106" s="437" t="s">
-        <v>1699</v>
-      </c>
+      <c r="B106" s="437"/>
+      <c r="C106" s="437"/>
       <c r="D106" s="295" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="E106" s="434" t="s">
         <v>24</v>
@@ -20901,7 +20934,7 @@
       <c r="B107" s="437"/>
       <c r="C107" s="437"/>
       <c r="D107" s="295" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="E107" s="434" t="s">
         <v>24</v>
@@ -20920,7 +20953,7 @@
       <c r="B108" s="437"/>
       <c r="C108" s="437"/>
       <c r="D108" s="295" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E108" s="434" t="s">
         <v>24</v>
@@ -20939,7 +20972,7 @@
       <c r="B109" s="437"/>
       <c r="C109" s="437"/>
       <c r="D109" s="295" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="E109" s="434" t="s">
         <v>24</v>
@@ -20958,7 +20991,7 @@
       <c r="B110" s="437"/>
       <c r="C110" s="437"/>
       <c r="D110" s="295" t="s">
-        <v>1730</v>
+        <v>1724</v>
       </c>
       <c r="E110" s="434" t="s">
         <v>24</v>
@@ -20977,7 +21010,7 @@
       <c r="B111" s="437"/>
       <c r="C111" s="437"/>
       <c r="D111" s="295" t="s">
-        <v>1724</v>
+        <v>1731</v>
       </c>
       <c r="E111" s="434" t="s">
         <v>24</v>
@@ -20992,23 +21025,8 @@
       </c>
     </row>
     <row r="112" spans="1:13" ht="17.250000" customHeight="1">
-      <c r="A112" s="437"/>
-      <c r="B112" s="437"/>
-      <c r="C112" s="437"/>
-      <c r="D112" s="295" t="s">
-        <v>1731</v>
-      </c>
-      <c r="E112" s="434" t="s">
-        <v>24</v>
-      </c>
-      <c r="F112" s="434"/>
-      <c r="G112" s="434"/>
-      <c r="H112" s="434"/>
-      <c r="I112" s="434"/>
-      <c r="J112" s="434"/>
-      <c r="K112" s="434" t="s">
-        <v>170</v>
-      </c>
+      <c r="A112" s="464"/>
+      <c r="E112" s="311"/>
     </row>
     <row r="113" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A113" s="464"/>
@@ -21020,39 +21038,47 @@
     </row>
     <row r="115" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A115" s="464"/>
-      <c r="E115" s="311"/>
     </row>
     <row r="116" spans="1:12" ht="17.250000" customHeight="1">
       <c r="A116" s="464"/>
     </row>
     <row r="117" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A117" s="464"/>
+      <c r="A117" s="463"/>
+      <c r="E117" s="311"/>
     </row>
     <row r="118" spans="1:12" ht="17.250000" customHeight="1">
-      <c r="A118" s="463"/>
-      <c r="E118" s="311"/>
       <c r="L118" s="463"/>
     </row>
-    <row r="121" spans="1:12" ht="40.200000" customHeight="1">
-      <c r="E121" s="311"/>
-    </row>
+    <row r="120" spans="1:12">
+      <c r="E120" s="311"/>
+    </row>
+    <row r="121" ht="40.200000" customHeight="1"/>
     <row r="122" ht="40.200000" customHeight="1"/>
-    <row r="123" ht="40.200000" customHeight="1"/>
-    <row r="124" spans="1:12" ht="47.700000" customHeight="1">
-      <c r="E124" s="311"/>
-    </row>
-    <row r="126" spans="1:12">
-      <c r="E126" s="311"/>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="E130" s="311"/>
-    </row>
-    <row r="132" spans="1:11">
-      <c r="E132" s="311"/>
+    <row r="123" spans="1:12" ht="40.200000" customHeight="1">
+      <c r="E123" s="311"/>
+    </row>
+    <row r="124" ht="47.700000" customHeight="1"/>
+    <row r="125" spans="1:12">
+      <c r="E125" s="311"/>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="E129" s="311"/>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="E131" s="311"/>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="B133" s="442"/>
+      <c r="C133" s="442"/>
+      <c r="F133" s="463"/>
+      <c r="G133" s="463"/>
+      <c r="H133" s="463"/>
+      <c r="I133" s="463"/>
+      <c r="J133" s="463"/>
+      <c r="K133" s="463"/>
     </row>
     <row r="134" spans="1:11">
-      <c r="B134" s="442"/>
-      <c r="C134" s="442"/>
+      <c r="C134" s="463"/>
       <c r="F134" s="463"/>
       <c r="G134" s="463"/>
       <c r="H134" s="463"/>
@@ -21133,6 +21159,7 @@
       <c r="K142" s="463"/>
     </row>
     <row r="143" spans="1:11">
+      <c r="A143" s="464"/>
       <c r="C143" s="463"/>
       <c r="F143" s="463"/>
       <c r="G143" s="463"/>
@@ -21142,7 +21169,7 @@
       <c r="K143" s="463"/>
     </row>
     <row r="144" spans="1:11" ht="28.500000">
-      <c r="A144" s="464"/>
+      <c r="A144" s="463"/>
       <c r="C144" s="463"/>
       <c r="F144" s="463"/>
       <c r="G144" s="463"/>
@@ -23174,12 +23201,6 @@
     <row r="347" spans="1:11" ht="17.250000" customHeight="1">
       <c r="A347" s="463"/>
       <c r="C347" s="463"/>
-      <c r="F347" s="463"/>
-      <c r="G347" s="463"/>
-      <c r="H347" s="463"/>
-      <c r="I347" s="463"/>
-      <c r="J347" s="463"/>
-      <c r="K347" s="463"/>
     </row>
     <row r="348" spans="1:11" ht="17.250000" customHeight="1">
       <c r="A348" s="463"/>
@@ -23187,7 +23208,6 @@
     </row>
     <row r="349" spans="1:11" ht="17.250000" customHeight="1">
       <c r="A349" s="463"/>
-      <c r="C349" s="463"/>
     </row>
     <row r="350" spans="1:11" ht="17.250000" customHeight="1">
       <c r="A350" s="463"/>
@@ -23200,6 +23220,7 @@
     </row>
     <row r="353" spans="1:2" ht="17.250000" customHeight="1">
       <c r="A353" s="463"/>
+      <c r="B353" s="311"/>
     </row>
     <row r="354" spans="1:2" ht="17.250000" customHeight="1">
       <c r="A354" s="463"/>
@@ -23207,23 +23228,22 @@
     </row>
     <row r="355" spans="1:2" ht="17.250000" customHeight="1">
       <c r="A355" s="463"/>
-      <c r="B355" s="311"/>
     </row>
     <row r="356" spans="1:2" ht="17.250000" customHeight="1">
       <c r="A356" s="463"/>
     </row>
     <row r="357" spans="1:2" ht="17.250000" customHeight="1">
       <c r="A357" s="463"/>
+      <c r="B357" s="311"/>
     </row>
     <row r="358" spans="1:2" ht="17.250000" customHeight="1">
       <c r="A358" s="463"/>
       <c r="B358" s="311"/>
     </row>
-    <row r="359" spans="1:2" ht="17.250000" customHeight="1">
-      <c r="A359" s="463"/>
-      <c r="B359" s="311"/>
-    </row>
-    <row r="360" ht="17.250000" customHeight="1"/>
+    <row r="359" ht="17.250000" customHeight="1"/>
+    <row r="360" spans="1:2" ht="17.250000" customHeight="1">
+      <c r="B360" s="311"/>
+    </row>
     <row r="361" spans="1:2" ht="17.250000" customHeight="1">
       <c r="B361" s="311"/>
     </row>
@@ -23236,11 +23256,12 @@
     <row r="364" spans="1:2" ht="17.250000" customHeight="1">
       <c r="B364" s="311"/>
     </row>
-    <row r="365" spans="1:2" ht="17.250000" customHeight="1">
-      <c r="B365" s="311"/>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="B367" s="311"/>
+    <row r="365" ht="17.250000" customHeight="1"/>
+    <row r="366" spans="1:2">
+      <c r="B366" s="311"/>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="B368" s="311"/>
     </row>
     <row r="369" spans="2:11" ht="54.000000" customHeight="1">
       <c r="B369" s="311"/>
@@ -23254,12 +23275,18 @@
     <row r="372" spans="2:11" ht="57.000000">
       <c r="B372" s="311"/>
     </row>
-    <row r="373" spans="2:11" ht="57.000000">
-      <c r="B373" s="311"/>
-    </row>
-    <row r="374" ht="42.750000" customHeight="1"/>
+    <row r="373" ht="57.000000" customHeight="1"/>
+    <row r="374" spans="2:11" ht="42.750000" customHeight="1">
+      <c r="B374" s="311"/>
+      <c r="E374" s="567"/>
+      <c r="F374" s="567"/>
+      <c r="G374" s="567"/>
+      <c r="H374" s="567"/>
+      <c r="I374" s="567"/>
+      <c r="J374" s="567"/>
+      <c r="K374" s="567"/>
+    </row>
     <row r="375" spans="2:11" ht="42.750000">
-      <c r="B375" s="311"/>
       <c r="E375" s="567"/>
       <c r="F375" s="567"/>
       <c r="G375" s="567"/>
@@ -23269,6 +23296,8 @@
       <c r="K375" s="567"/>
     </row>
     <row r="376" spans="2:11" ht="42.750000" customHeight="1">
+      <c r="B376" s="442"/>
+      <c r="C376" s="442"/>
       <c r="E376" s="567"/>
       <c r="F376" s="567"/>
       <c r="G376" s="567"/>
@@ -23377,6 +23406,7 @@
       <c r="K385" s="567"/>
     </row>
     <row r="386" spans="1:11">
+      <c r="A386" s="464"/>
       <c r="B386" s="442"/>
       <c r="C386" s="442"/>
       <c r="E386" s="567"/>
@@ -23655,6 +23685,7 @@
       <c r="A409" s="464"/>
       <c r="B409" s="442"/>
       <c r="C409" s="442"/>
+      <c r="D409" s="161"/>
       <c r="E409" s="567"/>
       <c r="F409" s="567"/>
       <c r="G409" s="567"/>
@@ -23668,13 +23699,13 @@
       <c r="B410" s="442"/>
       <c r="C410" s="442"/>
       <c r="D410" s="161"/>
-      <c r="E410" s="567"/>
-      <c r="F410" s="567"/>
-      <c r="G410" s="567"/>
-      <c r="H410" s="567"/>
-      <c r="I410" s="567"/>
-      <c r="J410" s="567"/>
-      <c r="K410" s="567"/>
+      <c r="E410" s="551"/>
+      <c r="F410" s="551"/>
+      <c r="G410" s="551"/>
+      <c r="H410" s="551"/>
+      <c r="I410" s="551"/>
+      <c r="J410" s="551"/>
+      <c r="K410" s="551"/>
     </row>
     <row r="411" spans="1:11" ht="17.250000" customHeight="1">
       <c r="A411" s="464"/>
@@ -23795,9 +23826,8 @@
     </row>
     <row r="420" spans="1:11" ht="17.250000" customHeight="1">
       <c r="A420" s="464"/>
-      <c r="B420" s="442"/>
-      <c r="C420" s="442"/>
-      <c r="D420" s="161"/>
+      <c r="B420" s="464"/>
+      <c r="C420" s="464"/>
       <c r="E420" s="551"/>
       <c r="F420" s="551"/>
       <c r="G420" s="551"/>
@@ -23810,6 +23840,7 @@
       <c r="A421" s="464"/>
       <c r="B421" s="464"/>
       <c r="C421" s="464"/>
+      <c r="D421" s="161"/>
       <c r="E421" s="551"/>
       <c r="F421" s="551"/>
       <c r="G421" s="551"/>
@@ -23822,7 +23853,6 @@
       <c r="A422" s="464"/>
       <c r="B422" s="464"/>
       <c r="C422" s="464"/>
-      <c r="D422" s="161"/>
       <c r="E422" s="551"/>
       <c r="F422" s="551"/>
       <c r="G422" s="551"/>
@@ -23847,6 +23877,7 @@
       <c r="A424" s="464"/>
       <c r="B424" s="464"/>
       <c r="C424" s="464"/>
+      <c r="D424" s="161"/>
       <c r="E424" s="551"/>
       <c r="F424" s="551"/>
       <c r="G424" s="551"/>
@@ -23859,7 +23890,6 @@
       <c r="A425" s="464"/>
       <c r="B425" s="464"/>
       <c r="C425" s="464"/>
-      <c r="D425" s="161"/>
       <c r="E425" s="551"/>
       <c r="F425" s="551"/>
       <c r="G425" s="551"/>
@@ -23968,13 +23998,13 @@
       <c r="A434" s="464"/>
       <c r="B434" s="464"/>
       <c r="C434" s="464"/>
-      <c r="E434" s="551"/>
-      <c r="F434" s="551"/>
-      <c r="G434" s="551"/>
-      <c r="H434" s="551"/>
-      <c r="I434" s="551"/>
-      <c r="J434" s="551"/>
-      <c r="K434" s="551"/>
+      <c r="E434" s="463"/>
+      <c r="F434" s="463"/>
+      <c r="G434" s="463"/>
+      <c r="H434" s="463"/>
+      <c r="I434" s="463"/>
+      <c r="J434" s="463"/>
+      <c r="K434" s="463"/>
     </row>
     <row r="435" spans="1:11">
       <c r="A435" s="464"/>
@@ -24299,6 +24329,7 @@
       <c r="A464" s="464"/>
       <c r="B464" s="464"/>
       <c r="C464" s="464"/>
+      <c r="D464" s="161"/>
       <c r="F464" s="463"/>
       <c r="G464" s="463"/>
       <c r="H464" s="463"/>
@@ -24430,7 +24461,6 @@
       <c r="A475" s="464"/>
       <c r="B475" s="464"/>
       <c r="C475" s="464"/>
-      <c r="D475" s="161"/>
       <c r="F475" s="463"/>
       <c r="G475" s="463"/>
       <c r="H475" s="463"/>
@@ -24442,6 +24472,7 @@
       <c r="A476" s="464"/>
       <c r="B476" s="464"/>
       <c r="C476" s="464"/>
+      <c r="D476" s="161"/>
       <c r="F476" s="463"/>
       <c r="G476" s="463"/>
       <c r="H476" s="463"/>
@@ -24453,7 +24484,6 @@
       <c r="A477" s="464"/>
       <c r="B477" s="464"/>
       <c r="C477" s="464"/>
-      <c r="D477" s="161"/>
       <c r="F477" s="463"/>
       <c r="G477" s="463"/>
       <c r="H477" s="463"/>
@@ -24476,6 +24506,7 @@
       <c r="A479" s="464"/>
       <c r="B479" s="464"/>
       <c r="C479" s="464"/>
+      <c r="D479" s="161"/>
       <c r="F479" s="463"/>
       <c r="G479" s="463"/>
       <c r="H479" s="463"/>
@@ -24487,7 +24518,7 @@
       <c r="A480" s="464"/>
       <c r="B480" s="464"/>
       <c r="C480" s="464"/>
-      <c r="D480" s="161"/>
+      <c r="D480" s="311"/>
       <c r="F480" s="463"/>
       <c r="G480" s="463"/>
       <c r="H480" s="463"/>
@@ -24642,17 +24673,17 @@
       <c r="A494" s="464"/>
       <c r="B494" s="464"/>
       <c r="C494" s="464"/>
-      <c r="F494" s="463"/>
-      <c r="G494" s="463"/>
-      <c r="H494" s="463"/>
-      <c r="I494" s="463"/>
-      <c r="J494" s="463"/>
-      <c r="K494" s="463"/>
+      <c r="F494" s="311"/>
+      <c r="G494" s="311"/>
+      <c r="H494" s="311"/>
+      <c r="I494" s="311"/>
+      <c r="J494" s="311"/>
+      <c r="K494" s="311"/>
     </row>
     <row r="495" spans="1:11">
       <c r="A495" s="464"/>
-      <c r="B495" s="464"/>
-      <c r="C495" s="464"/>
+      <c r="B495" s="463"/>
+      <c r="C495" s="311"/>
     </row>
     <row r="496" spans="1:11">
       <c r="A496" s="464"/>
@@ -24682,59 +24713,67 @@
       <c r="A504" s="464"/>
     </row>
     <row r="505" spans="1:1">
-      <c r="A505" s="464"/>
+      <c r="A505" s="311"/>
     </row>
   </sheetData>
-  <mergeCells count="128">
+  <mergeCells count="134">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:K2"/>
-    <mergeCell ref="A4:A52"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="C8:C13"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="C14:C21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="C24:C33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="B38:B49"/>
-    <mergeCell ref="C38:C49"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="A53:A73"/>
-    <mergeCell ref="B53:B61"/>
-    <mergeCell ref="C53:C61"/>
-    <mergeCell ref="D54:D60"/>
-    <mergeCell ref="E54:E60"/>
-    <mergeCell ref="F54:F60"/>
-    <mergeCell ref="G54:G60"/>
-    <mergeCell ref="H54:H60"/>
-    <mergeCell ref="I54:I60"/>
-    <mergeCell ref="J54:J60"/>
-    <mergeCell ref="K54:K60"/>
-    <mergeCell ref="B62:B73"/>
-    <mergeCell ref="C62:C73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="A77:A112"/>
-    <mergeCell ref="B77:B80"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="B81:B91"/>
-    <mergeCell ref="C81:C91"/>
-    <mergeCell ref="B92:B98"/>
-    <mergeCell ref="C92:C98"/>
-    <mergeCell ref="B99:B105"/>
-    <mergeCell ref="C99:C105"/>
-    <mergeCell ref="B106:B112"/>
-    <mergeCell ref="C106:C112"/>
-    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="A4:A51"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
+    <mergeCell ref="B15:B23"/>
+    <mergeCell ref="C15:C23"/>
+    <mergeCell ref="B25:B33"/>
+    <mergeCell ref="C25:C33"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B37:B48"/>
+    <mergeCell ref="C37:C48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="B52:B60"/>
+    <mergeCell ref="C52:C60"/>
+    <mergeCell ref="A52:A72"/>
+    <mergeCell ref="D53:D59"/>
+    <mergeCell ref="E53:E59"/>
+    <mergeCell ref="F53:F59"/>
+    <mergeCell ref="G53:G59"/>
+    <mergeCell ref="H53:H59"/>
+    <mergeCell ref="I53:I59"/>
+    <mergeCell ref="J53:J59"/>
+    <mergeCell ref="K53:K59"/>
+    <mergeCell ref="B61:B72"/>
+    <mergeCell ref="C61:C72"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="A76:A111"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="B80:B90"/>
+    <mergeCell ref="C80:C90"/>
+    <mergeCell ref="B91:B97"/>
+    <mergeCell ref="C91:C97"/>
+    <mergeCell ref="B98:B104"/>
+    <mergeCell ref="C98:C104"/>
+    <mergeCell ref="B105:B111"/>
+    <mergeCell ref="C105:C111"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="E374:K374"/>
     <mergeCell ref="E375:K375"/>
+    <mergeCell ref="B376:C376"/>
     <mergeCell ref="E376:K376"/>
     <mergeCell ref="B377:C377"/>
     <mergeCell ref="E377:K377"/>
@@ -24803,7 +24842,6 @@
     <mergeCell ref="B409:C409"/>
     <mergeCell ref="E409:K409"/>
     <mergeCell ref="B410:C410"/>
-    <mergeCell ref="E410:K410"/>
     <mergeCell ref="B411:C411"/>
     <mergeCell ref="B412:C412"/>
     <mergeCell ref="B413:C413"/>
@@ -24813,7 +24851,6 @@
     <mergeCell ref="B417:C417"/>
     <mergeCell ref="B418:C418"/>
     <mergeCell ref="B419:C419"/>
-    <mergeCell ref="B420:C420"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
